--- a/agriculture 56.xlsx
+++ b/agriculture 56.xlsx
@@ -20,10 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="67">
-  <si>
-    <t xml:space="preserve">Annual Growth Rate of State-wise Area Statistics of Rubber in India (1950-2020)</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="66">
   <si>
     <t xml:space="preserve">Year</t>
   </si>
@@ -231,11 +228,12 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
@@ -254,14 +252,6 @@
     </font>
     <font>
       <b val="true"/>
-      <sz val="14"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -277,33 +267,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
     <border diagonalUp="false" diagonalDown="false">
@@ -339,36 +308,24 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -393,606 +350,603 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D64"/>
-  <sheetFormatPr defaultColWidth="10.76953125" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:D1048576"/>
+  <sheetFormatPr defaultColWidth="10.78515625" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.56"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.3"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="18" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="28.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="3"/>
-    </row>
-    <row r="2" customFormat="false" ht="28.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="5" t="s">
+    </row>
+    <row r="2" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="s">
         <v>4</v>
       </c>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="6"/>
-      <c r="C3" s="6"/>
+      <c r="B3" s="4" t="n">
+        <v>0.907990314769976</v>
+      </c>
+      <c r="C3" s="4" t="n">
+        <v>5.09085372043447</v>
+      </c>
+      <c r="D3" s="5" t="n">
+        <v>4.51800957734749</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="7" t="n">
-        <v>0.907990314769976</v>
-      </c>
-      <c r="C4" s="7" t="n">
-        <v>5.09085372043447</v>
-      </c>
-      <c r="D4" s="8" t="n">
-        <v>4.51800957734749</v>
+      <c r="B4" s="4" t="n">
+        <v>-0.599880023995201</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>1.39303825852969</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>6.55378486055777</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="7" t="n">
-        <v>-0.599880023995201</v>
-      </c>
-      <c r="C5" s="7" t="n">
-        <v>1.39303825852969</v>
-      </c>
-      <c r="D5" s="8" t="n">
-        <v>6.55378486055777</v>
+      <c r="B5" s="4" t="n">
+        <v>-0.12070006035003</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>1.82846332866067</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>3.83249205458964</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="7" t="n">
-        <v>-0.12070006035003</v>
-      </c>
-      <c r="C6" s="7" t="n">
-        <v>1.82846332866067</v>
-      </c>
-      <c r="D6" s="8" t="n">
-        <v>3.83249205458964</v>
-      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="5"/>
     </row>
     <row r="7" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="8"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="5"/>
     </row>
     <row r="8" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="8"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="5"/>
     </row>
     <row r="9" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="8"/>
+      <c r="B9" s="4"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="5"/>
     </row>
     <row r="10" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8"/>
+      <c r="B10" s="4"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="5"/>
     </row>
     <row r="11" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="8"/>
+      <c r="B11" s="4"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="5"/>
     </row>
     <row r="12" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="8"/>
+      <c r="B12" s="4"/>
+      <c r="C12" s="4"/>
+      <c r="D12" s="5"/>
     </row>
     <row r="13" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="8"/>
+      <c r="B13" s="4"/>
+      <c r="C13" s="4"/>
+      <c r="D13" s="5"/>
     </row>
     <row r="14" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="8"/>
+      <c r="B14" s="4"/>
+      <c r="C14" s="4"/>
+      <c r="D14" s="5"/>
     </row>
     <row r="15" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="8"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="5"/>
     </row>
     <row r="16" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="8"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="5"/>
     </row>
     <row r="17" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="8"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="5"/>
     </row>
     <row r="18" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="8"/>
+      <c r="B18" s="4" t="n">
+        <v>2.53164556962025</v>
+      </c>
+      <c r="C18" s="4" t="n">
+        <v>1.35256988277728</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>0.819672131147541</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6" t="s">
+      <c r="A19" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B19" s="7" t="n">
-        <v>2.53164556962025</v>
-      </c>
-      <c r="C19" s="7" t="n">
-        <v>1.35256988277728</v>
-      </c>
-      <c r="D19" s="8" t="n">
-        <v>0.819672131147541</v>
+      <c r="B19" s="4" t="n">
+        <v>1.23456790123457</v>
+      </c>
+      <c r="C19" s="4" t="n">
+        <v>2.04626334519573</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>5.69105691056911</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B20" s="7" t="n">
-        <v>1.23456790123457</v>
-      </c>
-      <c r="C20" s="7" t="n">
-        <v>2.04626334519573</v>
-      </c>
-      <c r="D20" s="8" t="n">
-        <v>5.69105691056911</v>
+      <c r="B20" s="4" t="n">
+        <v>3.65853658536585</v>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>7.71578029642546</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>19.2307692307692</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="6" t="s">
+      <c r="A21" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="7" t="n">
-        <v>3.65853658536585</v>
-      </c>
-      <c r="C21" s="7" t="n">
-        <v>7.71578029642546</v>
-      </c>
-      <c r="D21" s="8" t="n">
-        <v>19.2307692307692</v>
+      <c r="B21" s="4" t="n">
+        <v>4.70588235294118</v>
+      </c>
+      <c r="C21" s="4" t="n">
+        <v>6.27276406313234</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>1.29032258064516</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="6" t="s">
+      <c r="A22" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="7" t="n">
-        <v>4.70588235294118</v>
-      </c>
-      <c r="C22" s="7" t="n">
-        <v>6.27276406313234</v>
-      </c>
-      <c r="D22" s="8" t="n">
-        <v>1.29032258064516</v>
+      <c r="B22" s="4" t="n">
+        <v>6.74157303370787</v>
+      </c>
+      <c r="C22" s="4" t="n">
+        <v>5.86443259710587</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>1.91082802547771</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="6" t="s">
+      <c r="A23" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B23" s="7" t="n">
-        <v>6.74157303370787</v>
-      </c>
-      <c r="C23" s="7" t="n">
-        <v>5.86443259710587</v>
-      </c>
-      <c r="D23" s="8" t="n">
-        <v>1.91082802547771</v>
+      <c r="B23" s="4" t="n">
+        <v>6.31578947368421</v>
+      </c>
+      <c r="C23" s="4" t="n">
+        <v>5.86330935251799</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>1.875</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="6" t="s">
+      <c r="A24" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B24" s="7" t="n">
-        <v>6.31578947368421</v>
-      </c>
-      <c r="C24" s="7" t="n">
-        <v>5.86330935251799</v>
-      </c>
-      <c r="D24" s="8" t="n">
-        <v>1.875</v>
+      <c r="B24" s="4" t="n">
+        <v>6.93069306930693</v>
+      </c>
+      <c r="C24" s="4" t="n">
+        <v>6.01427115188583</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>1.22699386503067</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="s">
+      <c r="A25" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B25" s="7" t="n">
-        <v>6.93069306930693</v>
-      </c>
-      <c r="C25" s="7" t="n">
-        <v>6.01427115188583</v>
-      </c>
-      <c r="D25" s="8" t="n">
-        <v>1.22699386503067</v>
+      <c r="B25" s="4" t="n">
+        <v>3.7037037037037</v>
+      </c>
+      <c r="C25" s="4" t="n">
+        <v>4.71153846153846</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>1.21212121212121</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
+      <c r="A26" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B26" s="7" t="n">
-        <v>3.7037037037037</v>
-      </c>
-      <c r="C26" s="7" t="n">
-        <v>4.71153846153846</v>
-      </c>
-      <c r="D26" s="8" t="n">
-        <v>1.21212121212121</v>
+      <c r="B26" s="4" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>4.86685032139578</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>0.598802395209581</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
+      <c r="A27" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B27" s="7" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="C27" s="7" t="n">
-        <v>4.86685032139578</v>
-      </c>
-      <c r="D27" s="8" t="n">
-        <v>0.598802395209581</v>
+      <c r="B27" s="4" t="n">
+        <v>4.20168067226891</v>
+      </c>
+      <c r="C27" s="4" t="n">
+        <v>3.61938120256859</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>0.595238095238095</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B28" s="7" t="n">
-        <v>4.20168067226891</v>
-      </c>
-      <c r="C28" s="7" t="n">
-        <v>3.61938120256859</v>
-      </c>
-      <c r="D28" s="8" t="n">
-        <v>0.595238095238095</v>
+      <c r="B28" s="4" t="n">
+        <v>3.2258064516129</v>
+      </c>
+      <c r="C28" s="4" t="n">
+        <v>3.29577464788732</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>0.591715976331361</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B29" s="7" t="n">
-        <v>3.2258064516129</v>
-      </c>
-      <c r="C29" s="7" t="n">
-        <v>3.29577464788732</v>
-      </c>
-      <c r="D29" s="8" t="n">
-        <v>0.591715976331361</v>
+      <c r="B29" s="4" t="n">
+        <v>3.125</v>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>2.75429506408508</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>0.588235294117647</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="6" t="s">
+      <c r="A30" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B30" s="7" t="n">
-        <v>3.125</v>
-      </c>
-      <c r="C30" s="7" t="n">
-        <v>2.75429506408508</v>
-      </c>
-      <c r="D30" s="8" t="n">
-        <v>0.588235294117647</v>
+      <c r="B30" s="4" t="n">
+        <v>6.06060606060606</v>
+      </c>
+      <c r="C30" s="4" t="n">
+        <v>8.22717622080679</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>0.584795321637427</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="6" t="s">
+      <c r="A31" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B31" s="7" t="n">
-        <v>6.06060606060606</v>
-      </c>
-      <c r="C31" s="7" t="n">
-        <v>8.22717622080679</v>
-      </c>
-      <c r="D31" s="8" t="n">
-        <v>0.584795321637427</v>
+      <c r="B31" s="4" t="n">
+        <v>2.85714285714286</v>
+      </c>
+      <c r="C31" s="4" t="n">
+        <v>2.79548798430603</v>
+      </c>
+      <c r="D31" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="6" t="s">
+      <c r="A32" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B32" s="7" t="n">
-        <v>2.85714285714286</v>
-      </c>
-      <c r="C32" s="7" t="n">
-        <v>2.79548798430603</v>
-      </c>
-      <c r="D32" s="8" t="n">
+      <c r="B32" s="4" t="n">
+        <v>1.38888888888889</v>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>2.31393129770992</v>
+      </c>
+      <c r="D32" s="5" t="n">
+        <v>0.581395348837209</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B33" s="4" t="n">
+        <v>2.05479452054794</v>
+      </c>
+      <c r="C33" s="4" t="n">
+        <v>1.91186756819772</v>
+      </c>
+      <c r="D33" s="5" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="B33" s="7" t="n">
-        <v>1.38888888888889</v>
-      </c>
-      <c r="C33" s="7" t="n">
-        <v>2.31393129770992</v>
-      </c>
-      <c r="D33" s="8" t="n">
-        <v>0.581395348837209</v>
-      </c>
-    </row>
     <row r="34" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6" t="s">
+      <c r="A34" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B34" s="7" t="n">
-        <v>2.05479452054794</v>
-      </c>
-      <c r="C34" s="7" t="n">
-        <v>1.91186756819772</v>
-      </c>
-      <c r="D34" s="8" t="n">
-        <v>0</v>
+      <c r="B34" s="4" t="n">
+        <v>0.671140939597315</v>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>1.41843971631206</v>
+      </c>
+      <c r="D34" s="5" t="n">
+        <v>0.578034682080925</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="6" t="s">
+      <c r="A35" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B35" s="7" t="n">
-        <v>0.671140939597315</v>
-      </c>
-      <c r="C35" s="7" t="n">
-        <v>1.41843971631206</v>
-      </c>
-      <c r="D35" s="8" t="n">
-        <v>0.578034682080925</v>
+      <c r="B35" s="4" t="n">
+        <v>8.66666666666667</v>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>1.28581096323032</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>2.8735632183908</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="6" t="s">
+      <c r="A36" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="7" t="n">
-        <v>8.66666666666667</v>
-      </c>
-      <c r="C36" s="7" t="n">
-        <v>1.28581096323032</v>
-      </c>
-      <c r="D36" s="8" t="n">
-        <v>2.8735632183908</v>
+      <c r="B36" s="4" t="n">
+        <v>6.13496932515337</v>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>1.46993318485523</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>1.67597765363129</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="6" t="s">
+      <c r="A37" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B37" s="7" t="n">
-        <v>6.13496932515337</v>
-      </c>
-      <c r="C37" s="7" t="n">
-        <v>1.46993318485523</v>
-      </c>
-      <c r="D37" s="8" t="n">
-        <v>1.67597765363129</v>
-      </c>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
     </row>
     <row r="38" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="6" t="s">
+      <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="6"/>
-      <c r="C38" s="6"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
     </row>
     <row r="39" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="6" t="s">
+      <c r="A39" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="6"/>
-      <c r="C39" s="6"/>
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
     </row>
     <row r="40" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="6" t="s">
+      <c r="A40" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
     </row>
     <row r="41" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="6" t="s">
+      <c r="A41" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B41" s="6"/>
-      <c r="C41" s="6"/>
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
     </row>
     <row r="42" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="6" t="s">
+      <c r="A42" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="B42" s="6"/>
-      <c r="C42" s="6"/>
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
     </row>
     <row r="43" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="6" t="s">
+      <c r="A43" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="B43" s="6"/>
-      <c r="C43" s="6"/>
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
     </row>
     <row r="44" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="6" t="s">
+      <c r="A44" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B44" s="6"/>
-      <c r="C44" s="6"/>
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
     </row>
     <row r="45" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="6" t="s">
+      <c r="A45" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="B45" s="6"/>
-      <c r="C45" s="6"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
     </row>
     <row r="46" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="6" t="s">
+      <c r="A46" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B46" s="6"/>
-      <c r="C46" s="6"/>
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
     </row>
     <row r="47" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="6" t="s">
+      <c r="A47" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B47" s="6"/>
-      <c r="C47" s="6"/>
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
     </row>
     <row r="48" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="6" t="s">
+      <c r="A48" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B48" s="6"/>
-      <c r="C48" s="6"/>
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
     </row>
     <row r="49" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="6" t="s">
+      <c r="A49" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="B49" s="6"/>
-      <c r="C49" s="6"/>
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
     </row>
     <row r="50" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="6" t="s">
+      <c r="A50" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="B50" s="6"/>
-      <c r="C50" s="6"/>
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
     </row>
     <row r="51" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="6" t="s">
+      <c r="A51" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="B51" s="6"/>
-      <c r="C51" s="6"/>
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
     </row>
     <row r="52" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="6" t="s">
+      <c r="A52" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="B52" s="6"/>
-      <c r="C52" s="6"/>
+      <c r="B52" s="3"/>
+      <c r="C52" s="3"/>
     </row>
     <row r="53" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="6" t="s">
+      <c r="A53" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="B53" s="6"/>
-      <c r="C53" s="6"/>
+      <c r="B53" s="3"/>
+      <c r="C53" s="3"/>
     </row>
     <row r="54" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="6" t="s">
+      <c r="A54" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B54" s="6"/>
-      <c r="C54" s="6"/>
+      <c r="B54" s="3"/>
+      <c r="C54" s="3"/>
     </row>
     <row r="55" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="6" t="s">
+      <c r="A55" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B55" s="6"/>
-      <c r="C55" s="6"/>
+      <c r="B55" s="3"/>
+      <c r="C55" s="3"/>
     </row>
     <row r="56" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="6" t="s">
+      <c r="A56" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="B56" s="6"/>
-      <c r="C56" s="6"/>
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
     </row>
     <row r="57" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="6" t="s">
+      <c r="A57" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B57" s="6"/>
-      <c r="C57" s="6"/>
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
     </row>
     <row r="58" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="6" t="s">
+      <c r="A58" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="B58" s="6"/>
-      <c r="C58" s="6"/>
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
     </row>
     <row r="59" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="6" t="s">
+      <c r="A59" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B59" s="6"/>
-      <c r="C59" s="6"/>
+      <c r="B59" s="3"/>
+      <c r="C59" s="3"/>
     </row>
     <row r="60" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="6" t="s">
+      <c r="A60" s="0" t="s">
         <v>62</v>
       </c>
-      <c r="B60" s="6"/>
-      <c r="C60" s="6"/>
     </row>
     <row r="61" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="0" t="s">
@@ -1009,11 +963,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="0" t="s">
-        <v>66</v>
-      </c>
-    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/agriculture 56.xlsx
+++ b/agriculture 56.xlsx
@@ -208,13 +208,13 @@
     <t xml:space="preserve">2019-20</t>
   </si>
   <si>
+    <t xml:space="preserve">Unit:- </t>
+  </si>
+  <si>
     <t xml:space="preserve">Source: EPWRF (Economic and Political Weekly Research Foundation) 1950-2020</t>
   </si>
   <si>
-    <t xml:space="preserve">Source Description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1962-63 to 2013-14: Plantation Crops: Rubber:-&gt; Directorate of Economics and Statistics, Dept. of Agriculture, Cooperation and Farmers Welfare, Ministry of Agriculture, Govt. of India</t>
+    <t xml:space="preserve">Source Description:- 1962-63 to 2013-14: Plantation Crops: Rubber:-&gt; Directorate of Economics and Statistics, Dept. of Agriculture, Cooperation and Farmers Welfare, Ministry of Agriculture, Govt. of India</t>
   </si>
   <si>
     <t xml:space="preserve">Directorate of Economics and Statistics, Dept. of Agriculture, Cooperation and Farmers Welfare, Ministry of Agriculture, Govt. of India</t>
@@ -228,7 +228,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -257,6 +257,11 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -308,13 +313,13 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -330,6 +335,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -350,14 +359,14 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D1048576"/>
-  <sheetFormatPr defaultColWidth="10.78515625" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:D63"/>
+  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.56"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.3"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="28.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -943,28 +952,45 @@
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
     </row>
-    <row r="60" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="0" t="s">
+    <row r="60" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="3" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="61" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A61" s="0" t="s">
+      <c r="B60" s="3"/>
+      <c r="C60" s="3"/>
+      <c r="D60" s="3"/>
+    </row>
+    <row r="61" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="6" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="62" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="0" t="s">
+      <c r="B61" s="6"/>
+      <c r="C61" s="6"/>
+      <c r="D61" s="6"/>
+    </row>
+    <row r="62" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="6" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="63" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="0" t="s">
+      <c r="B62" s="6"/>
+      <c r="C62" s="6"/>
+      <c r="D62" s="6"/>
+    </row>
+    <row r="63" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="6" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="B63" s="6"/>
+      <c r="C63" s="6"/>
+      <c r="D63" s="6"/>
+    </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A60:D60"/>
+    <mergeCell ref="A61:D61"/>
+    <mergeCell ref="A62:D62"/>
+    <mergeCell ref="A63:D63"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" useFirstPageNumber="true" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/agriculture 56.xlsx
+++ b/agriculture 56.xlsx
@@ -208,7 +208,7 @@
     <t xml:space="preserve">2019-20</t>
   </si>
   <si>
-    <t xml:space="preserve">Unit:- </t>
+    <t xml:space="preserve">Unit:- Percentage(%)</t>
   </si>
   <si>
     <t xml:space="preserve">Source: EPWRF (Economic and Political Weekly Research Foundation) 1950-2020</t>
@@ -228,7 +228,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -257,11 +257,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -338,7 +333,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -360,7 +355,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D63"/>
-  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.8125" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.56"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.3"/>

--- a/agriculture 56.xlsx
+++ b/agriculture 56.xlsx
@@ -208,7 +208,7 @@
     <t xml:space="preserve">2019-20</t>
   </si>
   <si>
-    <t xml:space="preserve">Unit:- Percentage(%)</t>
+    <t xml:space="preserve">Unit:- Percentage (%)</t>
   </si>
   <si>
     <t xml:space="preserve">Source: EPWRF (Economic and Political Weekly Research Foundation) 1950-2020</t>
@@ -355,7 +355,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D63"/>
-  <sheetFormatPr defaultColWidth="10.8125" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.82421875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.56"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13.3"/>
